--- a/assets/returns/Portfolio Returns.xlsx
+++ b/assets/returns/Portfolio Returns.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\FIN 203\FIN 203 Spring 2019\1 Historical Returns\2 Excercises\4 Portfolio Returns\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\1 Historical Returns\2 Excercises\6 Portfolio Returns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94F5FB2-D119-4893-9F51-4BBAAEBF8998}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C569B21-C327-44D1-897D-67B3A4D88CC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="16" r:id="rId1"/>
-    <sheet name="Questions" sheetId="17" r:id="rId2"/>
-    <sheet name="2 Asset Portfolio" sheetId="15" r:id="rId3"/>
+    <sheet name="2 Asset Portfolio" sheetId="15" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Mean</t>
   </si>
@@ -61,33 +61,6 @@
   <si>
     <t>Apple</t>
   </si>
-  <si>
-    <t>Assignment</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>WFU User Name</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Portfolio Returns</t>
-  </si>
-  <si>
-    <t>Both Apple and P&amp;G have expected returns of 5%. The portfolio also has an expected return of 5%. However, both Apple and P&amp;G have standard deviations of 10% yet the portfolio's standard deviation is not 10%. What explains these results?</t>
-  </si>
-  <si>
-    <t>What is the portfolio's standard deviation if the correlation between Apple and P&amp;G is 1.00?</t>
-  </si>
-  <si>
-    <t>Class Section</t>
-  </si>
 </sst>
 </file>
 
@@ -96,17 +69,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -127,27 +93,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -180,25 +125,25 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -214,32 +159,6 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -556,118 +475,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1559EBA-0EF7-4971-A3DE-1B5B54CAB4A7}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.54296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="16"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="16"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="16"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="16"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="23"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE70811A-E19A-4E64-B274-A5044E25EF41}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="2" width="64.6328125" style="18" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="17"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="19"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE818DD6-D48C-4117-8D6D-5EE524DBA019}">
   <dimension ref="A1:J121"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
